--- a/scenario réaliste/tech_ARC_reel.xlsx
+++ b/scenario réaliste/tech_ARC_reel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\scenario réaliste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F8AACC-760E-4E52-A458-13DE7166E99F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43E96D5-28AE-457E-AAB9-711EDE997F26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" firstSheet="1" activeTab="2" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="5" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
   </bookViews>
   <sheets>
     <sheet name="id_tech" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,8 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="66">
   <si>
     <t>HC</t>
   </si>
@@ -536,6 +538,175 @@
       <sheetData sheetId="25"/>
       <sheetData sheetId="26"/>
       <sheetData sheetId="27"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="LCIA_AD-f"/>
+      <sheetName val="IW+_end"/>
+      <sheetName val="LCI_AD-e"/>
+      <sheetName val="LCI_AD-f"/>
+      <sheetName val="Waste_characteristics"/>
+      <sheetName val="Parameters"/>
+      <sheetName val="LCI"/>
+      <sheetName val="LCI_AD-d"/>
+      <sheetName val="params_HC"/>
+      <sheetName val="LCI_AD-a"/>
+      <sheetName val="LCI_AD-c"/>
+      <sheetName val="LCI_HC"/>
+      <sheetName val="LCI_AD-b"/>
+      <sheetName val="LCIA_AD-b"/>
+      <sheetName val="LCIA_HC"/>
+      <sheetName val="LCIA_AD-c"/>
+      <sheetName val="LCIA_AD-d"/>
+      <sheetName val="LCIA_AD-e"/>
+      <sheetName val="Figures"/>
+      <sheetName val="Figures_transport"/>
+      <sheetName val="IW+f"/>
+      <sheetName val="LCIA_AD-a"/>
+      <sheetName val="LCIA_IC"/>
+      <sheetName val="LCI_IC"/>
+      <sheetName val="AD_a_end"/>
+      <sheetName val="impact_process_end"/>
+      <sheetName val="impact_process_mid"/>
+      <sheetName val="IW+_mid"/>
+      <sheetName val="IC_end"/>
+      <sheetName val="AD_a_mid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="102">
+          <cell r="AG102">
+            <v>-268.34014085734225</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="4">
+          <cell r="AG4">
+            <v>3.2363622700140461E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="42">
+          <cell r="E42">
+            <v>3876.4660709036466</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13">
+        <row r="99">
+          <cell r="AG99">
+            <v>-201.83380910205278</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="14">
+        <row r="46">
+          <cell r="AG46">
+            <v>-209.55449775755659</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="15">
+        <row r="80">
+          <cell r="AG80">
+            <v>-195.86519901883881</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="16">
+        <row r="98">
+          <cell r="AG98">
+            <v>-202.80044861589312</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="17">
+        <row r="83">
+          <cell r="AG83">
+            <v>-261.40489126028797</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20">
+        <row r="4">
+          <cell r="C4">
+            <v>0.189012950359117</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="21">
+        <row r="81">
+          <cell r="AG81">
+            <v>-194.89855950499845</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="22">
+        <row r="84">
+          <cell r="AG84">
+            <v>-140.00263317406106</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="id_tech"/>
+      <sheetName val="tech_lb"/>
+      <sheetName val="tech_ub"/>
+      <sheetName val="coproduct"/>
+      <sheetName val="subs_ratio"/>
+      <sheetName val="avoid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5">
+        <row r="6">
+          <cell r="H6">
+            <v>3876.4660709036466</v>
+          </cell>
+          <cell r="I6">
+            <v>3876.4660709036466</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -838,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA8F9C1E-CAC5-40F7-973A-3A444FB50574}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="27.6328125" customWidth="1"/>
@@ -909,6 +1080,30 @@
       </c>
       <c r="C6" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1417,13 +1612,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97EEBB80-2ABA-4FB4-95B0-0A371702950F}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1443,10 +1638,19 @@
         <v>23</v>
       </c>
       <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1465,11 +1669,20 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1477,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1489,11 +1702,22 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3">
+        <f>E3</f>
+        <v>0.15444202981514046</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>G3</f>
+        <v>0.15444202981514046</v>
+      </c>
+      <c r="J3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1514,11 +1738,21 @@
         <f>'[1]LCI_AD-c'!$E$26</f>
         <v>0.55448386609225153</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f>F4</f>
+        <v>0.55448386609225153</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1539,11 +1773,22 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f>'[2]LCI_AD-e'!$E$42</f>
+        <v>3876.4660709036466</v>
+      </c>
+      <c r="I5">
+        <f>'[2]LCI_AD-e'!$E$42</f>
+        <v>3876.4660709036466</v>
+      </c>
+      <c r="J5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1564,11 +1809,20 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1588,7 +1842,17 @@
         <f>'[1]LCI_AD-c'!$E$23</f>
         <v>131.83340888752835</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7">
+        <f>F7</f>
+        <v>131.83340888752835</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1727,13 +1991,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40B5BC93-5287-46F1-B8A8-81A7A63E9BBE}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1752,8 +2016,17 @@
       <c r="F1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1777,11 +2050,23 @@
         <f>+'[1]LCI_AD-c'!$E$34</f>
         <v>18.008880467039923</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2">
+        <f>'[1]LCI_AD-b'!$E$46</f>
+        <v>9.8391402733887965</v>
+      </c>
+      <c r="H2">
+        <f>+'[1]LCI_AD-c'!$E$34</f>
+        <v>18.008880467039923</v>
+      </c>
+      <c r="I2">
+        <f>'[1]LCI_AD-b'!$E$46</f>
+        <v>9.8391402733887965</v>
+      </c>
+      <c r="J2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1805,11 +2090,23 @@
         <f>+'[1]LCI_AD-c'!$E$35</f>
         <v>50.21783936417313</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3">
+        <f>+'[1]LCI_AD-b'!$E$47</f>
+        <v>31.938545835614104</v>
+      </c>
+      <c r="H3">
+        <f>+'[1]LCI_AD-c'!$E$35</f>
+        <v>50.21783936417313</v>
+      </c>
+      <c r="I3">
+        <f>+'[1]LCI_AD-b'!$E$47</f>
+        <v>31.938545835614104</v>
+      </c>
+      <c r="J3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1833,11 +2130,23 @@
         <f>+'[1]LCI_AD-c'!$E$36</f>
         <v>18.509017076560308</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4">
+        <f>+'[1]LCI_AD-b'!$E$48</f>
+        <v>2.8466868263749747</v>
+      </c>
+      <c r="H4">
+        <f>+'[1]LCI_AD-c'!$E$36</f>
+        <v>18.509017076560308</v>
+      </c>
+      <c r="I4">
+        <f>+'[1]LCI_AD-b'!$E$48</f>
+        <v>2.8466868263749747</v>
+      </c>
+      <c r="J4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1861,11 +2170,23 @@
         <f>+'[1]LCI_AD-c'!$E$37</f>
         <v>157.6259364797985</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5">
+        <f>E5</f>
+        <v>42.109844591027695</v>
+      </c>
+      <c r="H5">
+        <f>+'[1]LCI_AD-c'!$E$37</f>
+        <v>157.6259364797985</v>
+      </c>
+      <c r="I5">
+        <f>G5</f>
+        <v>42.109844591027695</v>
+      </c>
+      <c r="J5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1886,11 +2207,22 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f>[3]avoid!$H$6</f>
+        <v>3876.4660709036466</v>
+      </c>
+      <c r="I6">
+        <f>[3]avoid!$I$6</f>
+        <v>3876.4660709036466</v>
+      </c>
+      <c r="J6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1911,11 +2243,20 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1935,7 +2276,17 @@
         <f>+'[1]LCI_AD-c'!$E$38</f>
         <v>131.83340888752835</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8">
+        <f>F8</f>
+        <v>131.83340888752835</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
         <v>25</v>
       </c>
     </row>
